--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N123_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N123_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.60908382233225</v>
+        <v>11.31147612112899</v>
       </c>
       <c r="D2" t="n">
-        <v>65.21905634028566</v>
+        <v>10.59809665529642</v>
       </c>
       <c r="E2" t="n">
-        <v>9.539355208394959</v>
+        <v>1.550145221364181</v>
       </c>
       <c r="F2" t="n">
-        <v>24.32351989050549</v>
+        <v>3.952571982207143</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.53037340554233</v>
+        <v>8.21118567840063</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57201655927467</v>
+        <v>2.692952690882134</v>
       </c>
       <c r="E3" t="n">
-        <v>9.539355208394959</v>
+        <v>1.550145221364181</v>
       </c>
       <c r="F3" t="n">
-        <v>24.32351989050549</v>
+        <v>3.952571982207143</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
